--- a/PAMF_DIG F2 - monthly2026-07-10.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-10.xlsx
@@ -2166,7 +2166,7 @@
         <v>0.09</v>
       </c>
       <c r="N24" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>0.09</v>
       </c>
       <c r="N143" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>0.09</v>
       </c>
       <c r="N290" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O290" t="inlineStr">
         <is>
